--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.5544554455445545</v>
+        <v>0.5514018691588785</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4893617021276596</v>
+        <v>0.4929577464788732</v>
       </c>
       <c r="D2">
-        <v>0.5625</v>
+        <v>0.5496183206106871</v>
       </c>
       <c r="E2">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
